--- a/apptfg/static/bbdd/bbdd rapaces.xlsx
+++ b/apptfg/static/bbdd/bbdd rapaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paula.nieta\Documents\UNI Software\TFG - Técnicas de aprendizaje para la identificación de rapaces por restos óseos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA21BCE-19B3-4FF3-BBA4-049107C826F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88906595-FDE3-452C-A78C-51607AC8796C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="70">
   <si>
     <t>Media</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Águila Pescadora</t>
+  </si>
+  <si>
+    <t>Milano Negro</t>
+  </si>
+  <si>
+    <t>Milano Real</t>
   </si>
 </sst>
 </file>
@@ -33820,7 +33826,7 @@
         <v>13</v>
       </c>
       <c r="B584" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C584" s="6">
         <v>57.2</v>
@@ -33861,7 +33867,7 @@
         <v>39</v>
       </c>
       <c r="B585" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C585" s="6">
         <v>58.8</v>
@@ -33902,7 +33908,7 @@
         <v>411</v>
       </c>
       <c r="B586" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C586" s="6">
         <v>55.3</v>
@@ -33943,7 +33949,7 @@
         <v>412</v>
       </c>
       <c r="B587" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C587" s="6">
         <v>54.9</v>
@@ -33984,7 +33990,7 @@
         <v>413</v>
       </c>
       <c r="B588" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C588" s="6">
         <v>54.9</v>
@@ -34025,7 +34031,7 @@
         <v>414</v>
       </c>
       <c r="B589" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C589" s="6">
         <v>51.6</v>
@@ -34066,7 +34072,7 @@
         <v>415</v>
       </c>
       <c r="B590" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C590" s="6">
         <v>53.8</v>
@@ -34107,7 +34113,7 @@
         <v>416</v>
       </c>
       <c r="B591" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C591" s="6">
         <v>52.5</v>
@@ -34148,7 +34154,7 @@
         <v>417</v>
       </c>
       <c r="B592" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C592" s="6">
         <v>52.452913893713252</v>
@@ -34189,7 +34195,7 @@
         <v>418</v>
       </c>
       <c r="B593" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C593" s="6">
         <v>50.7</v>
@@ -34230,7 +34236,7 @@
         <v>419</v>
       </c>
       <c r="B594" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C594" s="6">
         <v>48.3</v>
@@ -34271,7 +34277,7 @@
         <v>420</v>
       </c>
       <c r="B595" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C595" s="6">
         <v>53.2</v>
@@ -34312,7 +34318,7 @@
         <v>421</v>
       </c>
       <c r="B596" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C596" s="6">
         <v>51.6</v>
@@ -34353,7 +34359,7 @@
         <v>422</v>
       </c>
       <c r="B597" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C597" s="6">
         <v>56</v>
@@ -34394,7 +34400,7 @@
         <v>423</v>
       </c>
       <c r="B598" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C598" s="6">
         <v>55.3</v>
@@ -34435,7 +34441,7 @@
         <v>424</v>
       </c>
       <c r="B599" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C599" s="6">
         <v>54.8</v>
@@ -34476,7 +34482,7 @@
         <v>425</v>
       </c>
       <c r="B600" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C600" s="6">
         <v>52.7</v>
@@ -34517,7 +34523,7 @@
         <v>426</v>
       </c>
       <c r="B601" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C601" s="6">
         <v>55.2</v>
@@ -34558,7 +34564,7 @@
         <v>427</v>
       </c>
       <c r="B602" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C602" s="6">
         <v>54.2</v>
@@ -34599,7 +34605,7 @@
         <v>428</v>
       </c>
       <c r="B603" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C603" s="6">
         <v>51.2</v>
@@ -34640,7 +34646,7 @@
         <v>429</v>
       </c>
       <c r="B604" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C604" s="6">
         <v>53.3</v>
@@ -34681,7 +34687,7 @@
         <v>430</v>
       </c>
       <c r="B605" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C605" s="6">
         <v>50.2</v>
@@ -34722,7 +34728,7 @@
         <v>431</v>
       </c>
       <c r="B606" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C606" s="6">
         <v>54.1</v>
@@ -34763,7 +34769,7 @@
         <v>432</v>
       </c>
       <c r="B607" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C607" s="6">
         <v>52.8</v>
@@ -34804,7 +34810,7 @@
         <v>433</v>
       </c>
       <c r="B608" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C608" s="6">
         <v>54.3</v>
@@ -34845,7 +34851,7 @@
         <v>434</v>
       </c>
       <c r="B609" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C609" s="6">
         <v>56.1</v>
@@ -34886,7 +34892,7 @@
         <v>435</v>
       </c>
       <c r="B610" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C610" s="6">
         <v>56.3</v>
@@ -34927,7 +34933,7 @@
         <v>436</v>
       </c>
       <c r="B611" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C611" s="6">
         <v>54.2</v>
@@ -34968,7 +34974,7 @@
         <v>437</v>
       </c>
       <c r="B612" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C612" s="6">
         <v>53.4</v>
@@ -35009,7 +35015,7 @@
         <v>438</v>
       </c>
       <c r="B613" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C613" s="6">
         <v>54.5</v>
@@ -35050,7 +35056,7 @@
         <v>439</v>
       </c>
       <c r="B614" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C614" s="6">
         <v>54.5</v>
@@ -35091,7 +35097,7 @@
         <v>440</v>
       </c>
       <c r="B615" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C615" s="6">
         <v>53.9</v>
@@ -35132,7 +35138,7 @@
         <v>441</v>
       </c>
       <c r="B616" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C616" s="6">
         <v>51.4</v>
@@ -35173,7 +35179,7 @@
         <v>442</v>
       </c>
       <c r="B617" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C617" s="6">
         <v>49.5</v>
@@ -35214,7 +35220,7 @@
         <v>443</v>
       </c>
       <c r="B618" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C618" s="6">
         <v>52.170776420567528</v>
@@ -35255,7 +35261,7 @@
         <v>444</v>
       </c>
       <c r="B619" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C619" s="6">
         <v>52.2</v>
@@ -35296,7 +35302,7 @@
         <v>445</v>
       </c>
       <c r="B620" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C620" s="6">
         <v>54.9</v>
@@ -35337,7 +35343,7 @@
         <v>446</v>
       </c>
       <c r="B621" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C621" s="6">
         <v>53.8</v>
@@ -35378,7 +35384,7 @@
         <v>447</v>
       </c>
       <c r="B622" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C622" s="6">
         <v>52.422773110471418</v>
@@ -35419,7 +35425,7 @@
         <v>448</v>
       </c>
       <c r="B623" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C623" s="6">
         <v>50.7</v>
@@ -35460,7 +35466,7 @@
         <v>449</v>
       </c>
       <c r="B624" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C624" s="6">
         <v>48.3</v>
@@ -35501,7 +35507,7 @@
         <v>450</v>
       </c>
       <c r="B625" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C625" s="6">
         <v>53.2</v>
@@ -35542,7 +35548,7 @@
         <v>451</v>
       </c>
       <c r="B626" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C626" s="6">
         <v>51.6</v>
@@ -35583,7 +35589,7 @@
         <v>452</v>
       </c>
       <c r="B627" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C627" s="6">
         <v>51.8</v>
@@ -35624,7 +35630,7 @@
         <v>453</v>
       </c>
       <c r="B628" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C628" s="6">
         <v>55.7</v>
@@ -35665,7 +35671,7 @@
         <v>454</v>
       </c>
       <c r="B629" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C629" s="6">
         <v>52.6</v>
@@ -35706,7 +35712,7 @@
         <v>455</v>
       </c>
       <c r="B630" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C630" s="6">
         <v>54</v>
@@ -35747,7 +35753,7 @@
         <v>456</v>
       </c>
       <c r="B631" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C631" s="6">
         <v>51.7</v>
@@ -35788,7 +35794,7 @@
         <v>457</v>
       </c>
       <c r="B632" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C632" s="6">
         <v>52.9</v>
@@ -35829,7 +35835,7 @@
         <v>458</v>
       </c>
       <c r="B633" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C633" s="6">
         <v>54.3</v>
@@ -35870,7 +35876,7 @@
         <v>459</v>
       </c>
       <c r="B634" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C634" s="6">
         <v>55.8</v>
@@ -35911,7 +35917,7 @@
         <v>1</v>
       </c>
       <c r="B635" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C635" s="6">
         <v>57.5</v>
@@ -35952,7 +35958,7 @@
         <v>2</v>
       </c>
       <c r="B636" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C636" s="6">
         <v>58.4</v>
@@ -35993,7 +35999,7 @@
         <v>3</v>
       </c>
       <c r="B637" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C637" s="6">
         <v>58.7</v>
@@ -36034,7 +36040,7 @@
         <v>4</v>
       </c>
       <c r="B638" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C638" s="6">
         <v>59</v>
@@ -36075,7 +36081,7 @@
         <v>5</v>
       </c>
       <c r="B639" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C639" s="6">
         <v>60.1</v>
@@ -36116,7 +36122,7 @@
         <v>6</v>
       </c>
       <c r="B640" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C640" s="6">
         <v>59.2</v>
@@ -36157,7 +36163,7 @@
         <v>7</v>
       </c>
       <c r="B641" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C641" s="6">
         <v>60.6</v>
@@ -36198,7 +36204,7 @@
         <v>8</v>
       </c>
       <c r="B642" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C642" s="6">
         <v>59.2</v>
@@ -36239,7 +36245,7 @@
         <v>9</v>
       </c>
       <c r="B643" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C643" s="6">
         <v>57.6</v>
@@ -36280,7 +36286,7 @@
         <v>10</v>
       </c>
       <c r="B644" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C644" s="6">
         <v>57.2</v>
@@ -36321,7 +36327,7 @@
         <v>11</v>
       </c>
       <c r="B645" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C645" s="6">
         <v>58.8</v>
@@ -36362,7 +36368,7 @@
         <v>12</v>
       </c>
       <c r="B646" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C646" s="6">
         <v>56.7</v>
@@ -36403,7 +36409,7 @@
         <v>14</v>
       </c>
       <c r="B647" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C647" s="6">
         <v>55.7</v>
@@ -36444,7 +36450,7 @@
         <v>15</v>
       </c>
       <c r="B648" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C648" s="6">
         <v>60.1</v>
@@ -36485,7 +36491,7 @@
         <v>16</v>
       </c>
       <c r="B649" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C649" s="6">
         <v>59.1</v>
@@ -36526,7 +36532,7 @@
         <v>17</v>
       </c>
       <c r="B650" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C650" s="6">
         <v>55.3</v>
@@ -36567,7 +36573,7 @@
         <v>18</v>
       </c>
       <c r="B651" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C651" s="6">
         <v>56.9</v>
@@ -36608,7 +36614,7 @@
         <v>19</v>
       </c>
       <c r="B652" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C652" s="6">
         <v>58.8</v>
@@ -36649,7 +36655,7 @@
         <v>20</v>
       </c>
       <c r="B653" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C653" s="6">
         <v>57</v>
@@ -36690,7 +36696,7 @@
         <v>21</v>
       </c>
       <c r="B654" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C654" s="6">
         <v>54.9</v>
@@ -36731,7 +36737,7 @@
         <v>22</v>
       </c>
       <c r="B655" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C655" s="6">
         <v>60.3</v>
@@ -36772,7 +36778,7 @@
         <v>23</v>
       </c>
       <c r="B656" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C656" s="6">
         <v>54.3</v>
@@ -36813,7 +36819,7 @@
         <v>24</v>
       </c>
       <c r="B657" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C657" s="6">
         <v>56.3</v>
@@ -36854,7 +36860,7 @@
         <v>25</v>
       </c>
       <c r="B658" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C658" s="6">
         <v>56.003155570647166</v>
@@ -36895,7 +36901,7 @@
         <v>26</v>
       </c>
       <c r="B659" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C659" s="6">
         <v>59.8</v>
@@ -36936,7 +36942,7 @@
         <v>27</v>
       </c>
       <c r="B660" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C660" s="6">
         <v>56</v>
@@ -36977,7 +36983,7 @@
         <v>28</v>
       </c>
       <c r="B661" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C661" s="6">
         <v>56.8</v>
@@ -37018,7 +37024,7 @@
         <v>29</v>
       </c>
       <c r="B662" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C662" s="6">
         <v>54.2</v>
@@ -37059,7 +37065,7 @@
         <v>30</v>
       </c>
       <c r="B663" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C663" s="6">
         <v>54.8</v>
@@ -37100,7 +37106,7 @@
         <v>31</v>
       </c>
       <c r="B664" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C664" s="6">
         <v>60.9</v>
@@ -37141,7 +37147,7 @@
         <v>32</v>
       </c>
       <c r="B665" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C665" s="6">
         <v>55.8</v>
@@ -37182,7 +37188,7 @@
         <v>33</v>
       </c>
       <c r="B666" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C666" s="6">
         <v>55.9</v>
@@ -37223,7 +37229,7 @@
         <v>34</v>
       </c>
       <c r="B667" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C667" s="6">
         <v>51.1</v>
@@ -37264,7 +37270,7 @@
         <v>35</v>
       </c>
       <c r="B668" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C668" s="6">
         <v>56.7</v>
@@ -37305,7 +37311,7 @@
         <v>36</v>
       </c>
       <c r="B669" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C669" s="6">
         <v>53.8</v>
@@ -37346,7 +37352,7 @@
         <v>37</v>
       </c>
       <c r="B670" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C670" s="6">
         <v>53.9</v>
@@ -37387,7 +37393,7 @@
         <v>38</v>
       </c>
       <c r="B671" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C671" s="6">
         <v>59.9</v>
@@ -37428,7 +37434,7 @@
         <v>40</v>
       </c>
       <c r="B672" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C672" s="6">
         <v>57.1</v>
